--- a/plan/content_plan.xlsx
+++ b/plan/content_plan.xlsx
@@ -1066,7 +1066,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 22 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/plan/content_plan.xlsx
+++ b/plan/content_plan.xlsx
@@ -1164,7 +1164,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Skipped (duplicate of breast pump types post)</t>
         </is>
       </c>
     </row>

--- a/plan/content_plan.xlsx
+++ b/plan/content_plan.xlsx
@@ -1115,7 +1115,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 24 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 25 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/plan/content_plan.xlsx
+++ b/plan/content_plan.xlsx
@@ -1311,7 +1311,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 26 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/plan/content_plan.xlsx
+++ b/plan/content_plan.xlsx
@@ -1360,7 +1360,7 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 27 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/plan/content_plan.xlsx
+++ b/plan/content_plan.xlsx
@@ -1406,10 +1406,14 @@
           <t>Pram folded</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>https://babysorted.com/article?slug=stroller-test-checklist</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 28 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -1455,10 +1459,14 @@
           <t>Toddler car seat</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>https://babysorted.com/article?slug=car-seat-groups-guide</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 29 Oct 2026</t>
         </is>
       </c>
     </row>

--- a/plan/content_plan.xlsx
+++ b/plan/content_plan.xlsx
@@ -1512,10 +1512,14 @@
           <t>Nursery set</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>https://babysorted.com/article?slug=safe-sleep-setup-checklist</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 30 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -1659,10 +1663,14 @@
           <t>Bottles</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>https://babysorted.com/article?slug=baby-bottle-buying-guide</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 31 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -1708,10 +1716,14 @@
           <t>Both models</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://babysorted.com/article?slug=travel-stroller-buying-guide</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Scheduled 1 Nov 2026</t>
         </is>
       </c>
     </row>
